--- a/planos-aulas/planos-de-aula.xlsx
+++ b/planos-aulas/planos-de-aula.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorgeotavio/projects/senai-desenvolvimento-sistemas/planos-aulas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E74116-6C2D-4146-8BBB-3082FAD2B000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EE79D4-C773-3A4A-9BF9-879215FEFEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="600" windowWidth="28800" windowHeight="16460" activeTab="1" xr2:uid="{7C4E5D0C-DB51-FB4E-97E7-56ACAED0E092}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16460" activeTab="1" xr2:uid="{7C4E5D0C-DB51-FB4E-97E7-56ACAED0E092}"/>
   </bookViews>
   <sheets>
     <sheet name="Plano de Aula - Modelo" sheetId="2" r:id="rId1"/>
-    <sheet name="23.27-03-2026" sheetId="3" r:id="rId2"/>
+    <sheet name="16.20-03-2026" sheetId="4" r:id="rId2"/>
+    <sheet name="23.27-03-2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="74">
   <si>
     <t>Plano de Aula</t>
   </si>
@@ -238,6 +239,32 @@
   </si>
   <si>
     <t>Questionário</t>
+  </si>
+  <si>
+    <t>Robótica</t>
+  </si>
+  <si>
+    <t>10 min</t>
+  </si>
+  <si>
+    <t>Relatório</t>
+  </si>
+  <si>
+    <t>O Aluno conseguir reconhecer as especificações técnicas e paradigmas conceito de internet das coisas.</t>
+  </si>
+  <si>
+    <t>O aluno conseguiu reconhecer as especificações técnicas e paradigmas conceito de internet das coisas.</t>
+  </si>
+  <si>
+    <t>O aluno deverá reconhecer as
+especificações técnicas e paradigmas
+conceito de internet das coisas.</t>
+  </si>
+  <si>
+    <t>Período de Virgência do Plano: 06 a 10/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data: 06/04/2026</t>
   </si>
 </sst>
 </file>
@@ -513,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -687,18 +714,27 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -755,6 +791,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1362,9 +1401,9 @@
       <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="F10" s="5" t="b">
         <v>0</v>
       </c>
@@ -1377,15 +1416,15 @@
       <c r="K10" s="16"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B11" s="59" t="s">
+      <c r="A11" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="F11" s="5" t="b">
         <v>0</v>
       </c>
@@ -1398,11 +1437,11 @@
       <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="58"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="F12" s="5" t="b">
         <v>0</v>
       </c>
@@ -1421,9 +1460,9 @@
       <c r="B13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="F13" s="5" t="b">
         <v>0</v>
       </c>
@@ -1436,15 +1475,15 @@
       <c r="K13" s="16"/>
     </row>
     <row r="14" spans="1:18" ht="67.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="62"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="15"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
@@ -1468,39 +1507,39 @@
       <c r="G15" s="44"/>
     </row>
     <row r="16" spans="1:18" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="53"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="55"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
       <c r="H16" s="17"/>
       <c r="I16" s="18"/>
       <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:11" s="20" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="51"/>
-      <c r="B17" s="52"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="55"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
       <c r="H17" s="17"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="51"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="58"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55" t="s">
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="56" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="17"/>
@@ -1508,25 +1547,25 @@
       <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="66"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="55"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="56"/>
       <c r="H19" s="17"/>
       <c r="I19" s="21"/>
       <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63"/>
-      <c r="B20" s="54"/>
+      <c r="A20" s="66"/>
+      <c r="B20" s="55"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="56"/>
       <c r="H20" s="17"/>
       <c r="I20" s="18"/>
       <c r="J20" s="19"/>
@@ -1539,44 +1578,44 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="65" t="s">
+      <c r="D21" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="66"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
       <c r="K21" s="23"/>
     </row>
     <row r="22" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="67"/>
-      <c r="B22" s="68"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="71"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="71"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="74"/>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
     </row>
     <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="65"/>
+      <c r="B23" s="68"/>
       <c r="C23" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="65" t="s">
+      <c r="D23" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="66"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="69"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
@@ -1588,11 +1627,11 @@
       <c r="B24" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="18"/>
@@ -1604,11 +1643,11 @@
       <c r="B25" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="55"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="18"/>
@@ -1620,11 +1659,11 @@
       <c r="B26" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="55"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="56"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="18"/>
@@ -1684,9 +1723,9 @@
       <c r="B30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
       <c r="F30" s="5" t="b">
         <v>0</v>
       </c>
@@ -1699,15 +1738,15 @@
       <c r="K30" s="16"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B31" s="59" t="s">
+      <c r="A31" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B31" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
       <c r="F31" s="5" t="b">
         <v>0</v>
       </c>
@@ -1720,11 +1759,11 @@
       <c r="K31" s="16"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="58"/>
-      <c r="B32" s="59"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
       <c r="F32" s="5" t="b">
         <v>0</v>
       </c>
@@ -1743,9 +1782,9 @@
       <c r="B33" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
       <c r="F33" s="5" t="b">
         <v>0</v>
       </c>
@@ -1758,15 +1797,15 @@
       <c r="K33" s="16"/>
     </row>
     <row r="34" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="60" t="s">
+      <c r="A34" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="62"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="15"/>
       <c r="I34" s="16"/>
       <c r="J34" s="16"/>
@@ -1790,39 +1829,39 @@
       <c r="G35" s="44"/>
     </row>
     <row r="36" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="51"/>
-      <c r="B36" s="52"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="53"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="55"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
       <c r="H36" s="17"/>
       <c r="I36" s="18"/>
       <c r="J36" s="19"/>
     </row>
     <row r="37" spans="1:11" s="20" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="51"/>
-      <c r="B37" s="52"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="58"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="55"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
       <c r="H37" s="17"/>
       <c r="I37" s="18"/>
       <c r="J37" s="19"/>
     </row>
     <row r="38" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="51"/>
-      <c r="B38" s="52"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="58"/>
       <c r="C38" s="8"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="55" t="s">
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="56" t="s">
         <v>29</v>
       </c>
       <c r="H38" s="17"/>
@@ -1830,25 +1869,25 @@
       <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="63"/>
-      <c r="B39" s="54"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="55"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="55"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="56"/>
       <c r="H39" s="17"/>
       <c r="I39" s="21"/>
       <c r="J39" s="19"/>
     </row>
     <row r="40" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="63"/>
-      <c r="B40" s="54"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="55"/>
       <c r="C40" s="8"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="55"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
       <c r="H40" s="17"/>
       <c r="I40" s="18"/>
       <c r="J40" s="19"/>
@@ -1861,44 +1900,44 @@
       <c r="C41" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="65" t="s">
+      <c r="D41" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="66"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69"/>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
       <c r="K41" s="23"/>
     </row>
     <row r="42" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="67"/>
-      <c r="B42" s="68"/>
+      <c r="A42" s="70"/>
+      <c r="B42" s="71"/>
       <c r="C42" s="24"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="71"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="74"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
       <c r="K42" s="23"/>
     </row>
     <row r="43" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="72" t="s">
+      <c r="A43" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="65"/>
+      <c r="B43" s="68"/>
       <c r="C43" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="65" t="s">
+      <c r="D43" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="66"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="69"/>
       <c r="H43" s="18"/>
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
@@ -1910,11 +1949,11 @@
       <c r="B44" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="54"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="55"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="56"/>
       <c r="I44" s="15"/>
       <c r="J44" s="15"/>
       <c r="K44" s="18"/>
@@ -1926,11 +1965,11 @@
       <c r="B45" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="64"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="55"/>
+      <c r="C45" s="67"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
       <c r="I45" s="15"/>
       <c r="J45" s="15"/>
       <c r="K45" s="18"/>
@@ -1942,11 +1981,11 @@
       <c r="B46" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="55"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56"/>
       <c r="I46" s="15"/>
       <c r="J46" s="15"/>
       <c r="K46" s="18"/>
@@ -2006,9 +2045,9 @@
       <c r="B50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
       <c r="F50" s="5" t="b">
         <v>0</v>
       </c>
@@ -2021,15 +2060,15 @@
       <c r="K50" s="16"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B51" s="59" t="s">
+      <c r="A51" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B51" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
       <c r="F51" s="5" t="b">
         <v>0</v>
       </c>
@@ -2042,11 +2081,11 @@
       <c r="K51" s="16"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="58"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
+      <c r="A52" s="61"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
       <c r="F52" s="5" t="b">
         <v>0</v>
       </c>
@@ -2065,9 +2104,9 @@
       <c r="B53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
       <c r="F53" s="5" t="b">
         <v>0</v>
       </c>
@@ -2080,15 +2119,15 @@
       <c r="K53" s="16"/>
     </row>
     <row r="54" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="60" t="s">
+      <c r="A54" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B54" s="61"/>
-      <c r="C54" s="61"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="62"/>
+      <c r="B54" s="64"/>
+      <c r="C54" s="64"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="65"/>
       <c r="H54" s="15"/>
       <c r="I54" s="16"/>
       <c r="J54" s="16"/>
@@ -2112,39 +2151,39 @@
       <c r="G55" s="44"/>
     </row>
     <row r="56" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="51"/>
-      <c r="B56" s="52"/>
+      <c r="A56" s="57"/>
+      <c r="B56" s="58"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="53" t="s">
+      <c r="D56" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="E56" s="53"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="55"/>
+      <c r="E56" s="76"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="56"/>
       <c r="H56" s="17"/>
       <c r="I56" s="18"/>
       <c r="J56" s="19"/>
     </row>
     <row r="57" spans="1:11" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="51"/>
-      <c r="B57" s="52"/>
+      <c r="A57" s="57"/>
+      <c r="B57" s="58"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="55"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="56"/>
       <c r="H57" s="17"/>
       <c r="I57" s="18"/>
       <c r="J57" s="19"/>
     </row>
     <row r="58" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="51"/>
-      <c r="B58" s="52"/>
+      <c r="A58" s="57"/>
+      <c r="B58" s="58"/>
       <c r="C58" s="8"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="55" t="s">
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="56" t="s">
         <v>29</v>
       </c>
       <c r="H58" s="17"/>
@@ -2152,25 +2191,25 @@
       <c r="J58" s="19"/>
     </row>
     <row r="59" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="63"/>
-      <c r="B59" s="54"/>
+      <c r="A59" s="66"/>
+      <c r="B59" s="55"/>
       <c r="C59" s="8"/>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="55"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="56"/>
       <c r="H59" s="17"/>
       <c r="I59" s="21"/>
       <c r="J59" s="19"/>
     </row>
     <row r="60" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="63"/>
-      <c r="B60" s="54"/>
+      <c r="A60" s="66"/>
+      <c r="B60" s="55"/>
       <c r="C60" s="8"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="55"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="56"/>
       <c r="H60" s="17"/>
       <c r="I60" s="18"/>
       <c r="J60" s="19"/>
@@ -2183,44 +2222,44 @@
       <c r="C61" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D61" s="65" t="s">
+      <c r="D61" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="66"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
       <c r="H61" s="23"/>
       <c r="I61" s="23"/>
       <c r="J61" s="23"/>
       <c r="K61" s="23"/>
     </row>
     <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="67"/>
-      <c r="B62" s="68"/>
+      <c r="A62" s="70"/>
+      <c r="B62" s="71"/>
       <c r="C62" s="24"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="70"/>
-      <c r="G62" s="71"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="74"/>
       <c r="H62" s="23"/>
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
       <c r="K62" s="23"/>
     </row>
     <row r="63" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="72" t="s">
+      <c r="A63" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B63" s="65"/>
+      <c r="B63" s="68"/>
       <c r="C63" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="65" t="s">
+      <c r="D63" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="65"/>
-      <c r="F63" s="65"/>
-      <c r="G63" s="66"/>
+      <c r="E63" s="68"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="69"/>
       <c r="H63" s="18"/>
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
@@ -2232,11 +2271,11 @@
       <c r="B64" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="64"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="55"/>
+      <c r="C64" s="67"/>
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="56"/>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
       <c r="K64" s="18"/>
@@ -2248,11 +2287,11 @@
       <c r="B65" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C65" s="64"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="55"/>
+      <c r="C65" s="67"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="56"/>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
       <c r="K65" s="18"/>
@@ -2264,11 +2303,11 @@
       <c r="B66" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C66" s="64"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="55"/>
+      <c r="C66" s="67"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="G66" s="56"/>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
       <c r="K66" s="18"/>
@@ -2286,10 +2325,10 @@
       <c r="K67" s="18"/>
     </row>
     <row r="68" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="73" t="s">
+      <c r="A68" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="74"/>
+      <c r="B68" s="78"/>
       <c r="C68" s="40" t="s">
         <v>42</v>
       </c>
@@ -2328,9 +2367,9 @@
       <c r="B70" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
+      <c r="C70" s="55"/>
+      <c r="D70" s="55"/>
+      <c r="E70" s="55"/>
       <c r="F70" s="5" t="b">
         <v>0</v>
       </c>
@@ -2343,15 +2382,15 @@
       <c r="K70" s="16"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A71" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B71" s="54" t="s">
+      <c r="A71" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="54"/>
-      <c r="D71" s="54"/>
-      <c r="E71" s="54"/>
+      <c r="C71" s="55"/>
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
       <c r="F71" s="5" t="b">
         <v>0</v>
       </c>
@@ -2364,11 +2403,11 @@
       <c r="K71" s="16"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="58"/>
-      <c r="B72" s="54"/>
-      <c r="C72" s="54"/>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
+      <c r="A72" s="61"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
       <c r="F72" s="5" t="b">
         <v>0</v>
       </c>
@@ -2387,9 +2426,9 @@
       <c r="B73" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
       <c r="F73" s="5" t="b">
         <v>0</v>
       </c>
@@ -2402,15 +2441,15 @@
       <c r="K73" s="16"/>
     </row>
     <row r="74" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="75" t="s">
+      <c r="A74" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="B74" s="76"/>
-      <c r="C74" s="76"/>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="77"/>
+      <c r="B74" s="80"/>
+      <c r="C74" s="80"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="80"/>
+      <c r="F74" s="80"/>
+      <c r="G74" s="81"/>
       <c r="H74" s="15"/>
       <c r="I74" s="16"/>
       <c r="J74" s="16"/>
@@ -2434,61 +2473,61 @@
       <c r="G75" s="44"/>
     </row>
     <row r="76" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="53"/>
+      <c r="A76" s="82"/>
+      <c r="B76" s="76"/>
       <c r="C76" s="8"/>
-      <c r="D76" s="53"/>
-      <c r="E76" s="53"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="79"/>
+      <c r="D76" s="76"/>
+      <c r="E76" s="76"/>
+      <c r="F76" s="76"/>
+      <c r="G76" s="83"/>
       <c r="H76" s="17"/>
       <c r="I76" s="18"/>
       <c r="J76" s="19"/>
     </row>
     <row r="77" spans="1:11" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78"/>
-      <c r="B77" s="53"/>
+      <c r="A77" s="82"/>
+      <c r="B77" s="76"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="53"/>
-      <c r="G77" s="79"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="76"/>
+      <c r="G77" s="83"/>
       <c r="H77" s="17"/>
       <c r="I77" s="18"/>
       <c r="J77" s="19"/>
     </row>
     <row r="78" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="78"/>
-      <c r="B78" s="53"/>
+      <c r="A78" s="82"/>
+      <c r="B78" s="76"/>
       <c r="C78" s="27"/>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="79"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="76"/>
+      <c r="G78" s="83"/>
       <c r="H78" s="17"/>
       <c r="I78" s="18"/>
       <c r="J78" s="19"/>
     </row>
     <row r="79" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="78"/>
-      <c r="B79" s="53"/>
+      <c r="A79" s="82"/>
+      <c r="B79" s="76"/>
       <c r="C79" s="27"/>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="79"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
+      <c r="F79" s="76"/>
+      <c r="G79" s="83"/>
       <c r="H79" s="17"/>
       <c r="I79" s="21"/>
       <c r="J79" s="19"/>
     </row>
     <row r="80" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="78"/>
-      <c r="B80" s="53"/>
+      <c r="A80" s="82"/>
+      <c r="B80" s="76"/>
       <c r="C80" s="27"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="79"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="76"/>
+      <c r="G80" s="83"/>
       <c r="H80" s="17"/>
       <c r="I80" s="18"/>
       <c r="J80" s="19"/>
@@ -2501,44 +2540,44 @@
       <c r="C81" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D81" s="65" t="s">
+      <c r="D81" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E81" s="65"/>
-      <c r="F81" s="65"/>
-      <c r="G81" s="66"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="69"/>
       <c r="H81" s="23"/>
       <c r="I81" s="23"/>
       <c r="J81" s="23"/>
       <c r="K81" s="23"/>
     </row>
     <row r="82" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="80"/>
-      <c r="B82" s="81"/>
+      <c r="A82" s="84"/>
+      <c r="B82" s="85"/>
       <c r="C82" s="28"/>
-      <c r="D82" s="70"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="70"/>
-      <c r="G82" s="71"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="73"/>
+      <c r="F82" s="73"/>
+      <c r="G82" s="74"/>
       <c r="H82" s="23"/>
       <c r="I82" s="23"/>
       <c r="J82" s="23"/>
       <c r="K82" s="23"/>
     </row>
     <row r="83" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="72" t="s">
+      <c r="A83" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B83" s="65"/>
+      <c r="B83" s="68"/>
       <c r="C83" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D83" s="65" t="s">
+      <c r="D83" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E83" s="65"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="66"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="69"/>
       <c r="H83" s="18"/>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
@@ -2550,11 +2589,11 @@
       <c r="B84" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C84" s="64"/>
-      <c r="D84" s="54"/>
-      <c r="E84" s="54"/>
-      <c r="F84" s="54"/>
-      <c r="G84" s="55"/>
+      <c r="C84" s="67"/>
+      <c r="D84" s="55"/>
+      <c r="E84" s="55"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="56"/>
       <c r="I84" s="15"/>
       <c r="J84" s="15"/>
       <c r="K84" s="18"/>
@@ -2566,11 +2605,11 @@
       <c r="B85" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C85" s="64"/>
-      <c r="D85" s="54"/>
-      <c r="E85" s="54"/>
-      <c r="F85" s="54"/>
-      <c r="G85" s="55"/>
+      <c r="C85" s="67"/>
+      <c r="D85" s="55"/>
+      <c r="E85" s="55"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="56"/>
       <c r="I85" s="15"/>
       <c r="J85" s="15"/>
       <c r="K85" s="18"/>
@@ -2582,11 +2621,11 @@
       <c r="B86" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C86" s="64"/>
-      <c r="D86" s="54"/>
-      <c r="E86" s="54"/>
-      <c r="F86" s="54"/>
-      <c r="G86" s="55"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="55"/>
+      <c r="E86" s="55"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="56"/>
       <c r="I86" s="15"/>
       <c r="J86" s="15"/>
       <c r="K86" s="18"/>
@@ -2604,10 +2643,10 @@
       <c r="K87" s="18"/>
     </row>
     <row r="88" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="73" t="s">
+      <c r="A88" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="B88" s="74"/>
+      <c r="B88" s="78"/>
       <c r="C88" s="40" t="s">
         <v>42</v>
       </c>
@@ -2646,9 +2685,9 @@
       <c r="B90" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C90" s="54"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="54"/>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55"/>
+      <c r="E90" s="55"/>
       <c r="F90" s="5" t="b">
         <v>0</v>
       </c>
@@ -2661,15 +2700,15 @@
       <c r="K90" s="16"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B91" s="54" t="s">
+      <c r="A91" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B91" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C91" s="54"/>
-      <c r="D91" s="54"/>
-      <c r="E91" s="54"/>
+      <c r="C91" s="55"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="55"/>
       <c r="F91" s="5" t="b">
         <v>0</v>
       </c>
@@ -2682,11 +2721,11 @@
       <c r="K91" s="16"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="58"/>
-      <c r="B92" s="54"/>
-      <c r="C92" s="54"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="54"/>
+      <c r="A92" s="61"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
       <c r="F92" s="5" t="b">
         <v>0</v>
       </c>
@@ -2705,9 +2744,9 @@
       <c r="B93" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C93" s="54"/>
-      <c r="D93" s="54"/>
-      <c r="E93" s="54"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
       <c r="F93" s="5" t="b">
         <v>0</v>
       </c>
@@ -2720,15 +2759,15 @@
       <c r="K93" s="16"/>
     </row>
     <row r="94" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="75" t="s">
+      <c r="A94" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="B94" s="76"/>
-      <c r="C94" s="76"/>
-      <c r="D94" s="76"/>
-      <c r="E94" s="76"/>
-      <c r="F94" s="76"/>
-      <c r="G94" s="77"/>
+      <c r="B94" s="80"/>
+      <c r="C94" s="80"/>
+      <c r="D94" s="80"/>
+      <c r="E94" s="80"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="81"/>
       <c r="H94" s="15"/>
       <c r="I94" s="16"/>
       <c r="J94" s="16"/>
@@ -2752,61 +2791,61 @@
       <c r="G95" s="44"/>
     </row>
     <row r="96" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="78"/>
-      <c r="B96" s="53"/>
+      <c r="A96" s="82"/>
+      <c r="B96" s="76"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="53"/>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="79"/>
+      <c r="D96" s="76"/>
+      <c r="E96" s="76"/>
+      <c r="F96" s="76"/>
+      <c r="G96" s="83"/>
       <c r="H96" s="17"/>
       <c r="I96" s="18"/>
       <c r="J96" s="19"/>
     </row>
     <row r="97" spans="1:12" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="78"/>
-      <c r="B97" s="53"/>
+      <c r="A97" s="82"/>
+      <c r="B97" s="76"/>
       <c r="C97" s="27"/>
-      <c r="D97" s="64"/>
-      <c r="E97" s="64"/>
-      <c r="F97" s="53"/>
-      <c r="G97" s="79"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="76"/>
+      <c r="G97" s="83"/>
       <c r="H97" s="17"/>
       <c r="I97" s="18"/>
       <c r="J97" s="19"/>
     </row>
     <row r="98" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="78"/>
-      <c r="B98" s="53"/>
+      <c r="A98" s="82"/>
+      <c r="B98" s="76"/>
       <c r="C98" s="27"/>
-      <c r="D98" s="64"/>
-      <c r="E98" s="64"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="79"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="76"/>
+      <c r="G98" s="83"/>
       <c r="H98" s="17"/>
       <c r="I98" s="18"/>
       <c r="J98" s="19"/>
     </row>
     <row r="99" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="78"/>
-      <c r="B99" s="53"/>
+      <c r="A99" s="82"/>
+      <c r="B99" s="76"/>
       <c r="C99" s="27"/>
-      <c r="D99" s="64"/>
-      <c r="E99" s="64"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="79"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="76"/>
+      <c r="G99" s="83"/>
       <c r="H99" s="17"/>
       <c r="I99" s="21"/>
       <c r="J99" s="19"/>
     </row>
     <row r="100" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="78"/>
-      <c r="B100" s="53"/>
+      <c r="A100" s="82"/>
+      <c r="B100" s="76"/>
       <c r="C100" s="27"/>
-      <c r="D100" s="64"/>
-      <c r="E100" s="64"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="79"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="76"/>
+      <c r="G100" s="83"/>
       <c r="H100" s="17"/>
       <c r="I100" s="18"/>
       <c r="J100" s="19"/>
@@ -2819,44 +2858,44 @@
       <c r="C101" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D101" s="65" t="s">
+      <c r="D101" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E101" s="65"/>
-      <c r="F101" s="65"/>
-      <c r="G101" s="66"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="69"/>
       <c r="H101" s="23"/>
       <c r="I101" s="23"/>
       <c r="J101" s="23"/>
       <c r="K101" s="23"/>
     </row>
     <row r="102" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="80"/>
-      <c r="B102" s="81"/>
+      <c r="A102" s="84"/>
+      <c r="B102" s="85"/>
       <c r="C102" s="28"/>
-      <c r="D102" s="70"/>
-      <c r="E102" s="70"/>
-      <c r="F102" s="70"/>
-      <c r="G102" s="71"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
+      <c r="F102" s="73"/>
+      <c r="G102" s="74"/>
       <c r="H102" s="23"/>
       <c r="I102" s="23"/>
       <c r="J102" s="23"/>
       <c r="K102" s="23"/>
     </row>
     <row r="103" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="72" t="s">
+      <c r="A103" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B103" s="65"/>
+      <c r="B103" s="68"/>
       <c r="C103" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D103" s="65" t="s">
+      <c r="D103" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E103" s="65"/>
-      <c r="F103" s="65"/>
-      <c r="G103" s="66"/>
+      <c r="E103" s="68"/>
+      <c r="F103" s="68"/>
+      <c r="G103" s="69"/>
       <c r="H103" s="18"/>
       <c r="I103" s="18"/>
       <c r="J103" s="18"/>
@@ -2868,11 +2907,11 @@
       <c r="B104" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C104" s="64"/>
-      <c r="D104" s="54"/>
-      <c r="E104" s="54"/>
-      <c r="F104" s="54"/>
-      <c r="G104" s="55"/>
+      <c r="C104" s="67"/>
+      <c r="D104" s="55"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="56"/>
       <c r="I104" s="15"/>
       <c r="J104" s="15"/>
       <c r="K104" s="18"/>
@@ -2884,11 +2923,11 @@
       <c r="B105" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C105" s="64"/>
-      <c r="D105" s="54"/>
-      <c r="E105" s="54"/>
-      <c r="F105" s="54"/>
-      <c r="G105" s="55"/>
+      <c r="C105" s="67"/>
+      <c r="D105" s="55"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="56"/>
       <c r="I105" s="15"/>
       <c r="J105" s="15"/>
       <c r="K105" s="18"/>
@@ -2900,36 +2939,36 @@
       <c r="B106" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C106" s="64"/>
-      <c r="D106" s="54"/>
-      <c r="E106" s="54"/>
-      <c r="F106" s="54"/>
-      <c r="G106" s="55"/>
+      <c r="C106" s="67"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="56"/>
       <c r="I106" s="15"/>
       <c r="J106" s="15"/>
       <c r="K106" s="18"/>
     </row>
     <row r="107" spans="1:12" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="75" t="s">
+      <c r="A107" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="B107" s="76"/>
-      <c r="C107" s="76"/>
-      <c r="D107" s="76"/>
-      <c r="E107" s="76"/>
-      <c r="F107" s="76"/>
-      <c r="G107" s="77"/>
+      <c r="B107" s="80"/>
+      <c r="C107" s="80"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="80"/>
+      <c r="F107" s="80"/>
+      <c r="G107" s="81"/>
     </row>
     <row r="108" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="60" t="s">
+      <c r="A108" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="B108" s="61"/>
-      <c r="C108" s="61"/>
-      <c r="D108" s="61"/>
-      <c r="E108" s="61"/>
-      <c r="F108" s="61"/>
-      <c r="G108" s="62"/>
+      <c r="B108" s="64"/>
+      <c r="C108" s="64"/>
+      <c r="D108" s="64"/>
+      <c r="E108" s="64"/>
+      <c r="F108" s="64"/>
+      <c r="G108" s="65"/>
       <c r="H108" s="23"/>
       <c r="I108" s="23"/>
       <c r="J108" s="23"/>
@@ -2937,13 +2976,13 @@
       <c r="L108" s="23"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A109" s="60"/>
-      <c r="B109" s="61"/>
-      <c r="C109" s="61"/>
-      <c r="D109" s="61"/>
-      <c r="E109" s="61"/>
-      <c r="F109" s="61"/>
-      <c r="G109" s="62"/>
+      <c r="A109" s="63"/>
+      <c r="B109" s="64"/>
+      <c r="C109" s="64"/>
+      <c r="D109" s="64"/>
+      <c r="E109" s="64"/>
+      <c r="F109" s="64"/>
+      <c r="G109" s="65"/>
       <c r="H109" s="23"/>
       <c r="I109" s="23"/>
       <c r="J109" s="23"/>
@@ -2951,13 +2990,13 @@
       <c r="L109" s="23"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A110" s="60"/>
-      <c r="B110" s="61"/>
-      <c r="C110" s="61"/>
-      <c r="D110" s="61"/>
-      <c r="E110" s="61"/>
-      <c r="F110" s="61"/>
-      <c r="G110" s="62"/>
+      <c r="A110" s="63"/>
+      <c r="B110" s="64"/>
+      <c r="C110" s="64"/>
+      <c r="D110" s="64"/>
+      <c r="E110" s="64"/>
+      <c r="F110" s="64"/>
+      <c r="G110" s="65"/>
       <c r="H110" s="23"/>
       <c r="I110" s="23"/>
       <c r="J110" s="23"/>
@@ -2965,13 +3004,13 @@
       <c r="L110" s="23"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A111" s="60"/>
-      <c r="B111" s="61"/>
-      <c r="C111" s="61"/>
-      <c r="D111" s="61"/>
-      <c r="E111" s="61"/>
-      <c r="F111" s="61"/>
-      <c r="G111" s="62"/>
+      <c r="A111" s="63"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="64"/>
+      <c r="D111" s="64"/>
+      <c r="E111" s="64"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="65"/>
       <c r="H111" s="23"/>
       <c r="I111" s="23"/>
       <c r="J111" s="23"/>
@@ -2979,13 +3018,13 @@
       <c r="L111" s="23"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A112" s="60"/>
-      <c r="B112" s="61"/>
-      <c r="C112" s="61"/>
-      <c r="D112" s="61"/>
-      <c r="E112" s="61"/>
-      <c r="F112" s="61"/>
-      <c r="G112" s="62"/>
+      <c r="A112" s="63"/>
+      <c r="B112" s="64"/>
+      <c r="C112" s="64"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="65"/>
       <c r="H112" s="23"/>
       <c r="I112" s="23"/>
       <c r="J112" s="23"/>
@@ -2993,99 +3032,2255 @@
       <c r="L112" s="23"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="82" t="s">
+      <c r="A113" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="B113" s="83"/>
-      <c r="C113" s="83"/>
-      <c r="D113" s="83"/>
-      <c r="E113" s="83"/>
-      <c r="F113" s="83"/>
-      <c r="G113" s="84"/>
+      <c r="B113" s="87"/>
+      <c r="C113" s="87"/>
+      <c r="D113" s="87"/>
+      <c r="E113" s="87"/>
+      <c r="F113" s="87"/>
+      <c r="G113" s="88"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="60" t="s">
+      <c r="A114" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B114" s="61"/>
-      <c r="C114" s="61"/>
-      <c r="D114" s="61"/>
-      <c r="E114" s="61"/>
-      <c r="F114" s="61"/>
-      <c r="G114" s="62"/>
+      <c r="B114" s="64"/>
+      <c r="C114" s="64"/>
+      <c r="D114" s="64"/>
+      <c r="E114" s="64"/>
+      <c r="F114" s="64"/>
+      <c r="G114" s="65"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B115" s="61" t="s">
+      <c r="B115" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="C115" s="61"/>
-      <c r="D115" s="61"/>
-      <c r="E115" s="61"/>
-      <c r="F115" s="61"/>
-      <c r="G115" s="62"/>
+      <c r="C115" s="64"/>
+      <c r="D115" s="64"/>
+      <c r="E115" s="64"/>
+      <c r="F115" s="64"/>
+      <c r="G115" s="65"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B116" s="61" t="s">
+      <c r="B116" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="C116" s="61"/>
-      <c r="D116" s="61"/>
-      <c r="E116" s="61"/>
-      <c r="F116" s="61"/>
-      <c r="G116" s="62"/>
+      <c r="C116" s="64"/>
+      <c r="D116" s="64"/>
+      <c r="E116" s="64"/>
+      <c r="F116" s="64"/>
+      <c r="G116" s="65"/>
     </row>
     <row r="117" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="60" t="s">
+      <c r="A117" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="B117" s="61"/>
-      <c r="C117" s="61"/>
-      <c r="D117" s="61"/>
-      <c r="E117" s="61"/>
-      <c r="F117" s="61"/>
-      <c r="G117" s="62"/>
+      <c r="B117" s="64"/>
+      <c r="C117" s="64"/>
+      <c r="D117" s="64"/>
+      <c r="E117" s="64"/>
+      <c r="F117" s="64"/>
+      <c r="G117" s="65"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="60"/>
-      <c r="B118" s="61"/>
-      <c r="C118" s="61"/>
-      <c r="D118" s="61"/>
-      <c r="E118" s="61"/>
-      <c r="F118" s="61"/>
-      <c r="G118" s="62"/>
+      <c r="A118" s="63"/>
+      <c r="B118" s="64"/>
+      <c r="C118" s="64"/>
+      <c r="D118" s="64"/>
+      <c r="E118" s="64"/>
+      <c r="F118" s="64"/>
+      <c r="G118" s="65"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="60"/>
-      <c r="B119" s="61"/>
-      <c r="C119" s="61"/>
-      <c r="D119" s="61"/>
-      <c r="E119" s="61"/>
-      <c r="F119" s="61"/>
-      <c r="G119" s="62"/>
+      <c r="A119" s="63"/>
+      <c r="B119" s="64"/>
+      <c r="C119" s="64"/>
+      <c r="D119" s="64"/>
+      <c r="E119" s="64"/>
+      <c r="F119" s="64"/>
+      <c r="G119" s="65"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="60"/>
-      <c r="B120" s="61"/>
-      <c r="C120" s="61"/>
-      <c r="D120" s="61"/>
-      <c r="E120" s="61"/>
-      <c r="F120" s="61"/>
-      <c r="G120" s="62"/>
+      <c r="A120" s="63"/>
+      <c r="B120" s="64"/>
+      <c r="C120" s="64"/>
+      <c r="D120" s="64"/>
+      <c r="E120" s="64"/>
+      <c r="F120" s="64"/>
+      <c r="G120" s="65"/>
     </row>
     <row r="121" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="85"/>
-      <c r="B121" s="86"/>
-      <c r="C121" s="86"/>
-      <c r="D121" s="86"/>
-      <c r="E121" s="86"/>
-      <c r="F121" s="86"/>
-      <c r="G121" s="87"/>
+      <c r="A121" s="89"/>
+      <c r="B121" s="90"/>
+      <c r="C121" s="90"/>
+      <c r="D121" s="90"/>
+      <c r="E121" s="90"/>
+      <c r="F121" s="90"/>
+      <c r="G121" s="91"/>
+    </row>
+  </sheetData>
+  <mergeCells count="195">
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C10:E13"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C30:E33"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C50:E53"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:G46"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:G66"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="D61:G61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="C70:E73"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="D84:G86"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="D81:G81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="D82:G82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="D83:G83"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C90:E93"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A94:G94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="D102:G102"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="A117:G121"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="D103:G103"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="D104:G106"/>
+    <mergeCell ref="A107:G107"/>
+    <mergeCell ref="A108:G112"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41AACDB3-4D2B-6D49-B6F5-DAAC374A76DB}">
+  <dimension ref="A1:R121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.5" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" customWidth="1"/>
+    <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.5" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" customWidth="1"/>
+    <col min="11" max="11" width="37.5" customWidth="1"/>
+    <col min="12" max="12" width="30.1640625" customWidth="1"/>
+    <col min="13" max="14" width="37.1640625" customWidth="1"/>
+    <col min="15" max="15" width="38.5" customWidth="1"/>
+    <col min="16" max="16" width="41.1640625" customWidth="1"/>
+    <col min="17" max="17" width="28.5" customWidth="1"/>
+    <col min="18" max="18" width="26.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="1:18" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+    </row>
+    <row r="3" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+    </row>
+    <row r="5" spans="1:18" ht="50.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+    </row>
+    <row r="6" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+    </row>
+    <row r="8" spans="1:18" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="44"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" spans="1:18" ht="67.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:18" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="44"/>
+    </row>
+    <row r="16" spans="1:18" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="52"/>
+      <c r="C16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="54"/>
+      <c r="F16" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="56"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
+    </row>
+    <row r="17" spans="1:11" s="20" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="57"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="57"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="66"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="66"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+    </row>
+    <row r="22" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="71"/>
+      <c r="C22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+    </row>
+    <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="68"/>
+      <c r="C23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="67">
+        <v>0</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="18"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="67"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="18"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="67"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="56"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="18"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="34"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="18"/>
+    </row>
+    <row r="28" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="44"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B31" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+    </row>
+    <row r="35" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="43"/>
+      <c r="C35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" s="44"/>
+    </row>
+    <row r="36" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="76"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="19"/>
+    </row>
+    <row r="37" spans="1:11" s="20" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="57"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="19"/>
+    </row>
+    <row r="38" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="57"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" s="17"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="19"/>
+    </row>
+    <row r="39" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="66"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="19"/>
+    </row>
+    <row r="40" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="66"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="19"/>
+    </row>
+    <row r="41" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="43"/>
+      <c r="C41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+    </row>
+    <row r="42" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="70"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+    </row>
+    <row r="43" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="68"/>
+      <c r="C43" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+    </row>
+    <row r="44" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="67"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="56"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="18"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="67"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="18"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="67"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="18"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="32"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="34"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="18"/>
+    </row>
+    <row r="48" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="39"/>
+      <c r="C48" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+    </row>
+    <row r="49" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="44"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B51" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" s="61"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="15"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+    </row>
+    <row r="54" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" s="64"/>
+      <c r="C54" s="64"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+    </row>
+    <row r="55" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="43"/>
+      <c r="C55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" s="44"/>
+    </row>
+    <row r="56" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="57"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" s="76"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="19"/>
+    </row>
+    <row r="57" spans="1:11" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="57"/>
+      <c r="B57" s="58"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="19"/>
+    </row>
+    <row r="58" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="57"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="19"/>
+    </row>
+    <row r="59" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="66"/>
+      <c r="B59" s="55"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="19"/>
+    </row>
+    <row r="60" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="66"/>
+      <c r="B60" s="55"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="19"/>
+    </row>
+    <row r="61" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" s="43"/>
+      <c r="C61" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D61" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="23"/>
+    </row>
+    <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="70"/>
+      <c r="B62" s="71"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="23"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="23"/>
+      <c r="K62" s="23"/>
+    </row>
+    <row r="63" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="68"/>
+      <c r="C63" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="68"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64" s="67"/>
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="56"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="18"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="56"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="18"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" s="67"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="G66" s="56"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="18"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" s="32"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="33"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="33"/>
+      <c r="F67" s="33"/>
+      <c r="G67" s="34"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="18"/>
+    </row>
+    <row r="68" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="78"/>
+      <c r="C68" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+    </row>
+    <row r="69" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="44"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="55"/>
+      <c r="D70" s="55"/>
+      <c r="E70" s="55"/>
+      <c r="F70" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="55"/>
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
+      <c r="F71" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" s="61"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+    </row>
+    <row r="74" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" s="80"/>
+      <c r="C74" s="80"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="80"/>
+      <c r="F74" s="80"/>
+      <c r="G74" s="81"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+    </row>
+    <row r="75" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="43"/>
+      <c r="C75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" s="43"/>
+      <c r="F75" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G75" s="44"/>
+    </row>
+    <row r="76" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="82"/>
+      <c r="B76" s="76"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="76"/>
+      <c r="E76" s="76"/>
+      <c r="F76" s="76"/>
+      <c r="G76" s="83"/>
+      <c r="H76" s="17"/>
+      <c r="I76" s="18"/>
+      <c r="J76" s="19"/>
+    </row>
+    <row r="77" spans="1:11" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="82"/>
+      <c r="B77" s="76"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="76"/>
+      <c r="G77" s="83"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="19"/>
+    </row>
+    <row r="78" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="82"/>
+      <c r="B78" s="76"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="76"/>
+      <c r="G78" s="83"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="19"/>
+    </row>
+    <row r="79" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="82"/>
+      <c r="B79" s="76"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
+      <c r="F79" s="76"/>
+      <c r="G79" s="83"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="21"/>
+      <c r="J79" s="19"/>
+    </row>
+    <row r="80" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="82"/>
+      <c r="B80" s="76"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="76"/>
+      <c r="G80" s="83"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="19"/>
+    </row>
+    <row r="81" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" s="43"/>
+      <c r="C81" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D81" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="23"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="23"/>
+      <c r="K81" s="23"/>
+    </row>
+    <row r="82" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="84"/>
+      <c r="B82" s="85"/>
+      <c r="C82" s="28"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="73"/>
+      <c r="F82" s="73"/>
+      <c r="G82" s="74"/>
+      <c r="H82" s="23"/>
+      <c r="I82" s="23"/>
+      <c r="J82" s="23"/>
+      <c r="K82" s="23"/>
+    </row>
+    <row r="83" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" s="68"/>
+      <c r="C83" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="69"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C84" s="67"/>
+      <c r="D84" s="55"/>
+      <c r="E84" s="55"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="56"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="18"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B85" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C85" s="67"/>
+      <c r="D85" s="55"/>
+      <c r="E85" s="55"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="56"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="15"/>
+      <c r="K85" s="18"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B86" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" s="67"/>
+      <c r="D86" s="55"/>
+      <c r="E86" s="55"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="56"/>
+      <c r="I86" s="15"/>
+      <c r="J86" s="15"/>
+      <c r="K86" s="18"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" s="32"/>
+      <c r="B87" s="33"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="33"/>
+      <c r="F87" s="33"/>
+      <c r="G87" s="34"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+      <c r="K87" s="18"/>
+    </row>
+    <row r="88" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="B88" s="78"/>
+      <c r="C88" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="41"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+    </row>
+    <row r="89" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B89" s="43"/>
+      <c r="C89" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="43"/>
+      <c r="E89" s="43"/>
+      <c r="F89" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" s="44"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55"/>
+      <c r="E90" s="55"/>
+      <c r="F90" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="15"/>
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="16"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B91" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="55"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="55"/>
+      <c r="F91" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" s="15"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92" s="61"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="15"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+      <c r="K92" s="16"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="15"/>
+      <c r="I93" s="16"/>
+      <c r="J93" s="16"/>
+      <c r="K93" s="16"/>
+    </row>
+    <row r="94" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B94" s="80"/>
+      <c r="C94" s="80"/>
+      <c r="D94" s="80"/>
+      <c r="E94" s="80"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="81"/>
+      <c r="H94" s="15"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+    </row>
+    <row r="95" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" s="43"/>
+      <c r="C95" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" s="43"/>
+      <c r="F95" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G95" s="44"/>
+    </row>
+    <row r="96" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="82"/>
+      <c r="B96" s="76"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="76"/>
+      <c r="E96" s="76"/>
+      <c r="F96" s="76"/>
+      <c r="G96" s="83"/>
+      <c r="H96" s="17"/>
+      <c r="I96" s="18"/>
+      <c r="J96" s="19"/>
+    </row>
+    <row r="97" spans="1:12" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="82"/>
+      <c r="B97" s="76"/>
+      <c r="C97" s="27"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="76"/>
+      <c r="G97" s="83"/>
+      <c r="H97" s="17"/>
+      <c r="I97" s="18"/>
+      <c r="J97" s="19"/>
+    </row>
+    <row r="98" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="82"/>
+      <c r="B98" s="76"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="76"/>
+      <c r="G98" s="83"/>
+      <c r="H98" s="17"/>
+      <c r="I98" s="18"/>
+      <c r="J98" s="19"/>
+    </row>
+    <row r="99" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="82"/>
+      <c r="B99" s="76"/>
+      <c r="C99" s="27"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="76"/>
+      <c r="G99" s="83"/>
+      <c r="H99" s="17"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="19"/>
+    </row>
+    <row r="100" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="82"/>
+      <c r="B100" s="76"/>
+      <c r="C100" s="27"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="76"/>
+      <c r="G100" s="83"/>
+      <c r="H100" s="17"/>
+      <c r="I100" s="18"/>
+      <c r="J100" s="19"/>
+    </row>
+    <row r="101" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" s="43"/>
+      <c r="C101" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D101" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="69"/>
+      <c r="H101" s="23"/>
+      <c r="I101" s="23"/>
+      <c r="J101" s="23"/>
+      <c r="K101" s="23"/>
+    </row>
+    <row r="102" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="84"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="28"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
+      <c r="F102" s="73"/>
+      <c r="G102" s="74"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+    </row>
+    <row r="103" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B103" s="68"/>
+      <c r="C103" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="68"/>
+      <c r="F103" s="68"/>
+      <c r="G103" s="69"/>
+      <c r="H103" s="18"/>
+      <c r="I103" s="18"/>
+      <c r="J103" s="18"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A104" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="B104" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="67"/>
+      <c r="D104" s="55"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="56"/>
+      <c r="I104" s="15"/>
+      <c r="J104" s="15"/>
+      <c r="K104" s="18"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A105" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B105" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="67"/>
+      <c r="D105" s="55"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="56"/>
+      <c r="I105" s="15"/>
+      <c r="J105" s="15"/>
+      <c r="K105" s="18"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A106" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B106" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C106" s="67"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="56"/>
+      <c r="I106" s="15"/>
+      <c r="J106" s="15"/>
+      <c r="K106" s="18"/>
+    </row>
+    <row r="107" spans="1:12" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="79" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" s="80"/>
+      <c r="C107" s="80"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="80"/>
+      <c r="F107" s="80"/>
+      <c r="G107" s="81"/>
+    </row>
+    <row r="108" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="B108" s="64"/>
+      <c r="C108" s="64"/>
+      <c r="D108" s="64"/>
+      <c r="E108" s="64"/>
+      <c r="F108" s="64"/>
+      <c r="G108" s="65"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
+      <c r="K108" s="23"/>
+      <c r="L108" s="23"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A109" s="63"/>
+      <c r="B109" s="64"/>
+      <c r="C109" s="64"/>
+      <c r="D109" s="64"/>
+      <c r="E109" s="64"/>
+      <c r="F109" s="64"/>
+      <c r="G109" s="65"/>
+      <c r="H109" s="23"/>
+      <c r="I109" s="23"/>
+      <c r="J109" s="23"/>
+      <c r="K109" s="23"/>
+      <c r="L109" s="23"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A110" s="63"/>
+      <c r="B110" s="64"/>
+      <c r="C110" s="64"/>
+      <c r="D110" s="64"/>
+      <c r="E110" s="64"/>
+      <c r="F110" s="64"/>
+      <c r="G110" s="65"/>
+      <c r="H110" s="23"/>
+      <c r="I110" s="23"/>
+      <c r="J110" s="23"/>
+      <c r="K110" s="23"/>
+      <c r="L110" s="23"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A111" s="63"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="64"/>
+      <c r="D111" s="64"/>
+      <c r="E111" s="64"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="65"/>
+      <c r="H111" s="23"/>
+      <c r="I111" s="23"/>
+      <c r="J111" s="23"/>
+      <c r="K111" s="23"/>
+      <c r="L111" s="23"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A112" s="63"/>
+      <c r="B112" s="64"/>
+      <c r="C112" s="64"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="65"/>
+      <c r="H112" s="23"/>
+      <c r="I112" s="23"/>
+      <c r="J112" s="23"/>
+      <c r="K112" s="23"/>
+      <c r="L112" s="23"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="B113" s="87"/>
+      <c r="C113" s="87"/>
+      <c r="D113" s="87"/>
+      <c r="E113" s="87"/>
+      <c r="F113" s="87"/>
+      <c r="G113" s="88"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="B114" s="64"/>
+      <c r="C114" s="64"/>
+      <c r="D114" s="64"/>
+      <c r="E114" s="64"/>
+      <c r="F114" s="64"/>
+      <c r="G114" s="65"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B115" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" s="64"/>
+      <c r="D115" s="64"/>
+      <c r="E115" s="64"/>
+      <c r="F115" s="64"/>
+      <c r="G115" s="65"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B116" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C116" s="64"/>
+      <c r="D116" s="64"/>
+      <c r="E116" s="64"/>
+      <c r="F116" s="64"/>
+      <c r="G116" s="65"/>
+    </row>
+    <row r="117" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="B117" s="64"/>
+      <c r="C117" s="64"/>
+      <c r="D117" s="64"/>
+      <c r="E117" s="64"/>
+      <c r="F117" s="64"/>
+      <c r="G117" s="65"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="63"/>
+      <c r="B118" s="64"/>
+      <c r="C118" s="64"/>
+      <c r="D118" s="64"/>
+      <c r="E118" s="64"/>
+      <c r="F118" s="64"/>
+      <c r="G118" s="65"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="63"/>
+      <c r="B119" s="64"/>
+      <c r="C119" s="64"/>
+      <c r="D119" s="64"/>
+      <c r="E119" s="64"/>
+      <c r="F119" s="64"/>
+      <c r="G119" s="65"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="63"/>
+      <c r="B120" s="64"/>
+      <c r="C120" s="64"/>
+      <c r="D120" s="64"/>
+      <c r="E120" s="64"/>
+      <c r="F120" s="64"/>
+      <c r="G120" s="65"/>
+    </row>
+    <row r="121" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="89"/>
+      <c r="B121" s="90"/>
+      <c r="C121" s="90"/>
+      <c r="D121" s="90"/>
+      <c r="E121" s="90"/>
+      <c r="F121" s="90"/>
+      <c r="G121" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="195">
@@ -3289,7 +5484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9179AD42-B734-7E47-8C31-632A8806CE61}">
   <dimension ref="A1:R121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3500,11 +5695,11 @@
       <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
       <c r="F10" s="5" t="b">
         <v>1</v>
       </c>
@@ -3517,15 +5712,15 @@
       <c r="K10" s="16"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="58" t="b">
+      <c r="A11" s="61" t="b">
         <v>1</v>
       </c>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
       <c r="F11" s="5" t="b">
         <v>0</v>
       </c>
@@ -3538,11 +5733,11 @@
       <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="58"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
       <c r="F12" s="5" t="b">
         <v>0</v>
       </c>
@@ -3561,9 +5756,9 @@
       <c r="B13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
       <c r="F13" s="5" t="b">
         <v>0</v>
       </c>
@@ -3576,15 +5771,15 @@
       <c r="K13" s="16"/>
     </row>
     <row r="14" spans="1:18" ht="67.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="62"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="15"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
@@ -3608,41 +5803,41 @@
       <c r="G15" s="44"/>
     </row>
     <row r="16" spans="1:18" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="53"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="55"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
       <c r="H16" s="17"/>
       <c r="I16" s="18"/>
       <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:11" s="20" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="51"/>
-      <c r="B17" s="52"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="55"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
       <c r="H17" s="17"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="51"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="58"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55" t="s">
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="56" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="17"/>
@@ -3650,25 +5845,25 @@
       <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="66"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="55"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="56"/>
       <c r="H19" s="17"/>
       <c r="I19" s="21"/>
       <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63"/>
-      <c r="B20" s="54"/>
+      <c r="A20" s="66"/>
+      <c r="B20" s="55"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="56"/>
       <c r="H20" s="17"/>
       <c r="I20" s="18"/>
       <c r="J20" s="19"/>
@@ -3681,48 +5876,48 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="65" t="s">
+      <c r="D21" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="66"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
       <c r="K21" s="23"/>
     </row>
     <row r="22" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="68"/>
+      <c r="B22" s="71"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="71"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="74"/>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
     </row>
     <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="65"/>
+      <c r="B23" s="68"/>
       <c r="C23" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="65" t="s">
+      <c r="D23" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="66"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="69"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
@@ -3734,13 +5929,13 @@
       <c r="B24" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="64">
+      <c r="C24" s="67">
         <v>5</v>
       </c>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="18"/>
@@ -3752,11 +5947,11 @@
       <c r="B25" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="55"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="18"/>
@@ -3768,11 +5963,11 @@
       <c r="B26" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="55"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="56"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="18"/>
@@ -3832,9 +6027,9 @@
       <c r="B30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
       <c r="F30" s="5" t="b">
         <v>0</v>
       </c>
@@ -3847,15 +6042,15 @@
       <c r="K30" s="16"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B31" s="59" t="s">
+      <c r="A31" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B31" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
       <c r="F31" s="5" t="b">
         <v>0</v>
       </c>
@@ -3868,11 +6063,11 @@
       <c r="K31" s="16"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="58"/>
-      <c r="B32" s="59"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
       <c r="F32" s="5" t="b">
         <v>0</v>
       </c>
@@ -3891,9 +6086,9 @@
       <c r="B33" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
       <c r="F33" s="5" t="b">
         <v>0</v>
       </c>
@@ -3906,15 +6101,15 @@
       <c r="K33" s="16"/>
     </row>
     <row r="34" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="60" t="s">
+      <c r="A34" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="62"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="15"/>
       <c r="I34" s="16"/>
       <c r="J34" s="16"/>
@@ -3938,39 +6133,39 @@
       <c r="G35" s="44"/>
     </row>
     <row r="36" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="51"/>
-      <c r="B36" s="52"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="53"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="55"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
       <c r="H36" s="17"/>
       <c r="I36" s="18"/>
       <c r="J36" s="19"/>
     </row>
     <row r="37" spans="1:11" s="20" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="51"/>
-      <c r="B37" s="52"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="58"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="55"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
       <c r="H37" s="17"/>
       <c r="I37" s="18"/>
       <c r="J37" s="19"/>
     </row>
     <row r="38" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="51"/>
-      <c r="B38" s="52"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="58"/>
       <c r="C38" s="8"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="55" t="s">
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="56" t="s">
         <v>29</v>
       </c>
       <c r="H38" s="17"/>
@@ -3978,25 +6173,25 @@
       <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="63"/>
-      <c r="B39" s="54"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="55"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="55"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="56"/>
       <c r="H39" s="17"/>
       <c r="I39" s="21"/>
       <c r="J39" s="19"/>
     </row>
     <row r="40" spans="1:11" s="20" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="63"/>
-      <c r="B40" s="54"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="55"/>
       <c r="C40" s="8"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="55"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
       <c r="H40" s="17"/>
       <c r="I40" s="18"/>
       <c r="J40" s="19"/>
@@ -4009,44 +6204,44 @@
       <c r="C41" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="65" t="s">
+      <c r="D41" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="66"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69"/>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
       <c r="K41" s="23"/>
     </row>
     <row r="42" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="67"/>
-      <c r="B42" s="68"/>
+      <c r="A42" s="70"/>
+      <c r="B42" s="71"/>
       <c r="C42" s="24"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="71"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="74"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
       <c r="K42" s="23"/>
     </row>
     <row r="43" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="72" t="s">
+      <c r="A43" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="65"/>
+      <c r="B43" s="68"/>
       <c r="C43" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="65" t="s">
+      <c r="D43" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="66"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="69"/>
       <c r="H43" s="18"/>
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
@@ -4058,11 +6253,11 @@
       <c r="B44" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="54"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="55"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="56"/>
       <c r="I44" s="15"/>
       <c r="J44" s="15"/>
       <c r="K44" s="18"/>
@@ -4074,11 +6269,11 @@
       <c r="B45" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="64"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="55"/>
+      <c r="C45" s="67"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
       <c r="I45" s="15"/>
       <c r="J45" s="15"/>
       <c r="K45" s="18"/>
@@ -4090,11 +6285,11 @@
       <c r="B46" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="55"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56"/>
       <c r="I46" s="15"/>
       <c r="J46" s="15"/>
       <c r="K46" s="18"/>
@@ -4154,9 +6349,9 @@
       <c r="B50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
       <c r="F50" s="5" t="b">
         <v>0</v>
       </c>
@@ -4169,15 +6364,15 @@
       <c r="K50" s="16"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B51" s="59" t="s">
+      <c r="A51" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B51" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
       <c r="F51" s="5" t="b">
         <v>0</v>
       </c>
@@ -4190,11 +6385,11 @@
       <c r="K51" s="16"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="58"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
+      <c r="A52" s="61"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
       <c r="F52" s="5" t="b">
         <v>0</v>
       </c>
@@ -4213,9 +6408,9 @@
       <c r="B53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
       <c r="F53" s="5" t="b">
         <v>0</v>
       </c>
@@ -4228,15 +6423,15 @@
       <c r="K53" s="16"/>
     </row>
     <row r="54" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="60" t="s">
+      <c r="A54" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B54" s="61"/>
-      <c r="C54" s="61"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="62"/>
+      <c r="B54" s="64"/>
+      <c r="C54" s="64"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="65"/>
       <c r="H54" s="15"/>
       <c r="I54" s="16"/>
       <c r="J54" s="16"/>
@@ -4260,39 +6455,39 @@
       <c r="G55" s="44"/>
     </row>
     <row r="56" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="51"/>
-      <c r="B56" s="52"/>
+      <c r="A56" s="57"/>
+      <c r="B56" s="58"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="53" t="s">
+      <c r="D56" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="E56" s="53"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="55"/>
+      <c r="E56" s="76"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="56"/>
       <c r="H56" s="17"/>
       <c r="I56" s="18"/>
       <c r="J56" s="19"/>
     </row>
     <row r="57" spans="1:11" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="51"/>
-      <c r="B57" s="52"/>
+      <c r="A57" s="57"/>
+      <c r="B57" s="58"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="55"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="56"/>
       <c r="H57" s="17"/>
       <c r="I57" s="18"/>
       <c r="J57" s="19"/>
     </row>
     <row r="58" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="51"/>
-      <c r="B58" s="52"/>
+      <c r="A58" s="57"/>
+      <c r="B58" s="58"/>
       <c r="C58" s="8"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="55" t="s">
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="56" t="s">
         <v>29</v>
       </c>
       <c r="H58" s="17"/>
@@ -4300,25 +6495,25 @@
       <c r="J58" s="19"/>
     </row>
     <row r="59" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="63"/>
-      <c r="B59" s="54"/>
+      <c r="A59" s="66"/>
+      <c r="B59" s="55"/>
       <c r="C59" s="8"/>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="55"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="56"/>
       <c r="H59" s="17"/>
       <c r="I59" s="21"/>
       <c r="J59" s="19"/>
     </row>
     <row r="60" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="63"/>
-      <c r="B60" s="54"/>
+      <c r="A60" s="66"/>
+      <c r="B60" s="55"/>
       <c r="C60" s="8"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="55"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="56"/>
       <c r="H60" s="17"/>
       <c r="I60" s="18"/>
       <c r="J60" s="19"/>
@@ -4331,44 +6526,44 @@
       <c r="C61" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D61" s="65" t="s">
+      <c r="D61" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="66"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
       <c r="H61" s="23"/>
       <c r="I61" s="23"/>
       <c r="J61" s="23"/>
       <c r="K61" s="23"/>
     </row>
     <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="67"/>
-      <c r="B62" s="68"/>
+      <c r="A62" s="70"/>
+      <c r="B62" s="71"/>
       <c r="C62" s="24"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="70"/>
-      <c r="G62" s="71"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="74"/>
       <c r="H62" s="23"/>
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
       <c r="K62" s="23"/>
     </row>
     <row r="63" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="72" t="s">
+      <c r="A63" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B63" s="65"/>
+      <c r="B63" s="68"/>
       <c r="C63" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="65" t="s">
+      <c r="D63" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="65"/>
-      <c r="F63" s="65"/>
-      <c r="G63" s="66"/>
+      <c r="E63" s="68"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="69"/>
       <c r="H63" s="18"/>
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
@@ -4380,11 +6575,11 @@
       <c r="B64" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="64"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="55"/>
+      <c r="C64" s="67"/>
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="56"/>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
       <c r="K64" s="18"/>
@@ -4396,11 +6591,11 @@
       <c r="B65" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C65" s="64"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="55"/>
+      <c r="C65" s="67"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="56"/>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
       <c r="K65" s="18"/>
@@ -4412,11 +6607,11 @@
       <c r="B66" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C66" s="64"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="55"/>
+      <c r="C66" s="67"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="G66" s="56"/>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
       <c r="K66" s="18"/>
@@ -4434,10 +6629,10 @@
       <c r="K67" s="18"/>
     </row>
     <row r="68" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="73" t="s">
+      <c r="A68" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="74"/>
+      <c r="B68" s="78"/>
       <c r="C68" s="40" t="s">
         <v>42</v>
       </c>
@@ -4476,9 +6671,9 @@
       <c r="B70" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
+      <c r="C70" s="55"/>
+      <c r="D70" s="55"/>
+      <c r="E70" s="55"/>
       <c r="F70" s="5" t="b">
         <v>0</v>
       </c>
@@ -4491,15 +6686,15 @@
       <c r="K70" s="16"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A71" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B71" s="54" t="s">
+      <c r="A71" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="54"/>
-      <c r="D71" s="54"/>
-      <c r="E71" s="54"/>
+      <c r="C71" s="55"/>
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
       <c r="F71" s="5" t="b">
         <v>0</v>
       </c>
@@ -4512,11 +6707,11 @@
       <c r="K71" s="16"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="58"/>
-      <c r="B72" s="54"/>
-      <c r="C72" s="54"/>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
+      <c r="A72" s="61"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
       <c r="F72" s="5" t="b">
         <v>0</v>
       </c>
@@ -4535,9 +6730,9 @@
       <c r="B73" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
       <c r="F73" s="5" t="b">
         <v>0</v>
       </c>
@@ -4550,15 +6745,15 @@
       <c r="K73" s="16"/>
     </row>
     <row r="74" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="75" t="s">
+      <c r="A74" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="B74" s="76"/>
-      <c r="C74" s="76"/>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="77"/>
+      <c r="B74" s="80"/>
+      <c r="C74" s="80"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="80"/>
+      <c r="F74" s="80"/>
+      <c r="G74" s="81"/>
       <c r="H74" s="15"/>
       <c r="I74" s="16"/>
       <c r="J74" s="16"/>
@@ -4582,61 +6777,61 @@
       <c r="G75" s="44"/>
     </row>
     <row r="76" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="53"/>
+      <c r="A76" s="82"/>
+      <c r="B76" s="76"/>
       <c r="C76" s="8"/>
-      <c r="D76" s="53"/>
-      <c r="E76" s="53"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="79"/>
+      <c r="D76" s="76"/>
+      <c r="E76" s="76"/>
+      <c r="F76" s="76"/>
+      <c r="G76" s="83"/>
       <c r="H76" s="17"/>
       <c r="I76" s="18"/>
       <c r="J76" s="19"/>
     </row>
     <row r="77" spans="1:11" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78"/>
-      <c r="B77" s="53"/>
+      <c r="A77" s="82"/>
+      <c r="B77" s="76"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="53"/>
-      <c r="G77" s="79"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="76"/>
+      <c r="G77" s="83"/>
       <c r="H77" s="17"/>
       <c r="I77" s="18"/>
       <c r="J77" s="19"/>
     </row>
     <row r="78" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="78"/>
-      <c r="B78" s="53"/>
+      <c r="A78" s="82"/>
+      <c r="B78" s="76"/>
       <c r="C78" s="27"/>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="79"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="76"/>
+      <c r="G78" s="83"/>
       <c r="H78" s="17"/>
       <c r="I78" s="18"/>
       <c r="J78" s="19"/>
     </row>
     <row r="79" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="78"/>
-      <c r="B79" s="53"/>
+      <c r="A79" s="82"/>
+      <c r="B79" s="76"/>
       <c r="C79" s="27"/>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="79"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
+      <c r="F79" s="76"/>
+      <c r="G79" s="83"/>
       <c r="H79" s="17"/>
       <c r="I79" s="21"/>
       <c r="J79" s="19"/>
     </row>
     <row r="80" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="78"/>
-      <c r="B80" s="53"/>
+      <c r="A80" s="82"/>
+      <c r="B80" s="76"/>
       <c r="C80" s="27"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="79"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="76"/>
+      <c r="G80" s="83"/>
       <c r="H80" s="17"/>
       <c r="I80" s="18"/>
       <c r="J80" s="19"/>
@@ -4649,44 +6844,44 @@
       <c r="C81" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D81" s="65" t="s">
+      <c r="D81" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E81" s="65"/>
-      <c r="F81" s="65"/>
-      <c r="G81" s="66"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="69"/>
       <c r="H81" s="23"/>
       <c r="I81" s="23"/>
       <c r="J81" s="23"/>
       <c r="K81" s="23"/>
     </row>
     <row r="82" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="80"/>
-      <c r="B82" s="81"/>
+      <c r="A82" s="84"/>
+      <c r="B82" s="85"/>
       <c r="C82" s="28"/>
-      <c r="D82" s="70"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="70"/>
-      <c r="G82" s="71"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="73"/>
+      <c r="F82" s="73"/>
+      <c r="G82" s="74"/>
       <c r="H82" s="23"/>
       <c r="I82" s="23"/>
       <c r="J82" s="23"/>
       <c r="K82" s="23"/>
     </row>
     <row r="83" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="72" t="s">
+      <c r="A83" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B83" s="65"/>
+      <c r="B83" s="68"/>
       <c r="C83" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D83" s="65" t="s">
+      <c r="D83" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E83" s="65"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="66"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="69"/>
       <c r="H83" s="18"/>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
@@ -4698,11 +6893,11 @@
       <c r="B84" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C84" s="64"/>
-      <c r="D84" s="54"/>
-      <c r="E84" s="54"/>
-      <c r="F84" s="54"/>
-      <c r="G84" s="55"/>
+      <c r="C84" s="67"/>
+      <c r="D84" s="55"/>
+      <c r="E84" s="55"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="56"/>
       <c r="I84" s="15"/>
       <c r="J84" s="15"/>
       <c r="K84" s="18"/>
@@ -4714,11 +6909,11 @@
       <c r="B85" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C85" s="64"/>
-      <c r="D85" s="54"/>
-      <c r="E85" s="54"/>
-      <c r="F85" s="54"/>
-      <c r="G85" s="55"/>
+      <c r="C85" s="67"/>
+      <c r="D85" s="55"/>
+      <c r="E85" s="55"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="56"/>
       <c r="I85" s="15"/>
       <c r="J85" s="15"/>
       <c r="K85" s="18"/>
@@ -4730,11 +6925,11 @@
       <c r="B86" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C86" s="64"/>
-      <c r="D86" s="54"/>
-      <c r="E86" s="54"/>
-      <c r="F86" s="54"/>
-      <c r="G86" s="55"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="55"/>
+      <c r="E86" s="55"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="56"/>
       <c r="I86" s="15"/>
       <c r="J86" s="15"/>
       <c r="K86" s="18"/>
@@ -4752,10 +6947,10 @@
       <c r="K87" s="18"/>
     </row>
     <row r="88" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="73" t="s">
+      <c r="A88" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="B88" s="74"/>
+      <c r="B88" s="78"/>
       <c r="C88" s="40" t="s">
         <v>42</v>
       </c>
@@ -4794,9 +6989,9 @@
       <c r="B90" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C90" s="54"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="54"/>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55"/>
+      <c r="E90" s="55"/>
       <c r="F90" s="5" t="b">
         <v>0</v>
       </c>
@@ -4809,15 +7004,15 @@
       <c r="K90" s="16"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B91" s="54" t="s">
+      <c r="A91" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B91" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C91" s="54"/>
-      <c r="D91" s="54"/>
-      <c r="E91" s="54"/>
+      <c r="C91" s="55"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="55"/>
       <c r="F91" s="5" t="b">
         <v>0</v>
       </c>
@@ -4830,11 +7025,11 @@
       <c r="K91" s="16"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="58"/>
-      <c r="B92" s="54"/>
-      <c r="C92" s="54"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="54"/>
+      <c r="A92" s="61"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
       <c r="F92" s="5" t="b">
         <v>0</v>
       </c>
@@ -4853,9 +7048,9 @@
       <c r="B93" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C93" s="54"/>
-      <c r="D93" s="54"/>
-      <c r="E93" s="54"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
       <c r="F93" s="5" t="b">
         <v>0</v>
       </c>
@@ -4868,15 +7063,15 @@
       <c r="K93" s="16"/>
     </row>
     <row r="94" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="75" t="s">
+      <c r="A94" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="B94" s="76"/>
-      <c r="C94" s="76"/>
-      <c r="D94" s="76"/>
-      <c r="E94" s="76"/>
-      <c r="F94" s="76"/>
-      <c r="G94" s="77"/>
+      <c r="B94" s="80"/>
+      <c r="C94" s="80"/>
+      <c r="D94" s="80"/>
+      <c r="E94" s="80"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="81"/>
       <c r="H94" s="15"/>
       <c r="I94" s="16"/>
       <c r="J94" s="16"/>
@@ -4900,61 +7095,61 @@
       <c r="G95" s="44"/>
     </row>
     <row r="96" spans="1:11" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="78"/>
-      <c r="B96" s="53"/>
+      <c r="A96" s="82"/>
+      <c r="B96" s="76"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="53"/>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="79"/>
+      <c r="D96" s="76"/>
+      <c r="E96" s="76"/>
+      <c r="F96" s="76"/>
+      <c r="G96" s="83"/>
       <c r="H96" s="17"/>
       <c r="I96" s="18"/>
       <c r="J96" s="19"/>
     </row>
     <row r="97" spans="1:12" s="20" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="78"/>
-      <c r="B97" s="53"/>
+      <c r="A97" s="82"/>
+      <c r="B97" s="76"/>
       <c r="C97" s="27"/>
-      <c r="D97" s="64"/>
-      <c r="E97" s="64"/>
-      <c r="F97" s="53"/>
-      <c r="G97" s="79"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="76"/>
+      <c r="G97" s="83"/>
       <c r="H97" s="17"/>
       <c r="I97" s="18"/>
       <c r="J97" s="19"/>
     </row>
     <row r="98" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="78"/>
-      <c r="B98" s="53"/>
+      <c r="A98" s="82"/>
+      <c r="B98" s="76"/>
       <c r="C98" s="27"/>
-      <c r="D98" s="64"/>
-      <c r="E98" s="64"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="79"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="76"/>
+      <c r="G98" s="83"/>
       <c r="H98" s="17"/>
       <c r="I98" s="18"/>
       <c r="J98" s="19"/>
     </row>
     <row r="99" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="78"/>
-      <c r="B99" s="53"/>
+      <c r="A99" s="82"/>
+      <c r="B99" s="76"/>
       <c r="C99" s="27"/>
-      <c r="D99" s="64"/>
-      <c r="E99" s="64"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="79"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="76"/>
+      <c r="G99" s="83"/>
       <c r="H99" s="17"/>
       <c r="I99" s="21"/>
       <c r="J99" s="19"/>
     </row>
     <row r="100" spans="1:12" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="78"/>
-      <c r="B100" s="53"/>
+      <c r="A100" s="82"/>
+      <c r="B100" s="76"/>
       <c r="C100" s="27"/>
-      <c r="D100" s="64"/>
-      <c r="E100" s="64"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="79"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="76"/>
+      <c r="G100" s="83"/>
       <c r="H100" s="17"/>
       <c r="I100" s="18"/>
       <c r="J100" s="19"/>
@@ -4967,44 +7162,44 @@
       <c r="C101" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D101" s="65" t="s">
+      <c r="D101" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E101" s="65"/>
-      <c r="F101" s="65"/>
-      <c r="G101" s="66"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="69"/>
       <c r="H101" s="23"/>
       <c r="I101" s="23"/>
       <c r="J101" s="23"/>
       <c r="K101" s="23"/>
     </row>
     <row r="102" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="80"/>
-      <c r="B102" s="81"/>
+      <c r="A102" s="84"/>
+      <c r="B102" s="85"/>
       <c r="C102" s="28"/>
-      <c r="D102" s="70"/>
-      <c r="E102" s="70"/>
-      <c r="F102" s="70"/>
-      <c r="G102" s="71"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
+      <c r="F102" s="73"/>
+      <c r="G102" s="74"/>
       <c r="H102" s="23"/>
       <c r="I102" s="23"/>
       <c r="J102" s="23"/>
       <c r="K102" s="23"/>
     </row>
     <row r="103" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="72" t="s">
+      <c r="A103" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B103" s="65"/>
+      <c r="B103" s="68"/>
       <c r="C103" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D103" s="65" t="s">
+      <c r="D103" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E103" s="65"/>
-      <c r="F103" s="65"/>
-      <c r="G103" s="66"/>
+      <c r="E103" s="68"/>
+      <c r="F103" s="68"/>
+      <c r="G103" s="69"/>
       <c r="H103" s="18"/>
       <c r="I103" s="18"/>
       <c r="J103" s="18"/>
@@ -5016,11 +7211,11 @@
       <c r="B104" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C104" s="64"/>
-      <c r="D104" s="54"/>
-      <c r="E104" s="54"/>
-      <c r="F104" s="54"/>
-      <c r="G104" s="55"/>
+      <c r="C104" s="67"/>
+      <c r="D104" s="55"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="56"/>
       <c r="I104" s="15"/>
       <c r="J104" s="15"/>
       <c r="K104" s="18"/>
@@ -5032,11 +7227,11 @@
       <c r="B105" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C105" s="64"/>
-      <c r="D105" s="54"/>
-      <c r="E105" s="54"/>
-      <c r="F105" s="54"/>
-      <c r="G105" s="55"/>
+      <c r="C105" s="67"/>
+      <c r="D105" s="55"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="56"/>
       <c r="I105" s="15"/>
       <c r="J105" s="15"/>
       <c r="K105" s="18"/>
@@ -5048,36 +7243,36 @@
       <c r="B106" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C106" s="64"/>
-      <c r="D106" s="54"/>
-      <c r="E106" s="54"/>
-      <c r="F106" s="54"/>
-      <c r="G106" s="55"/>
+      <c r="C106" s="67"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="56"/>
       <c r="I106" s="15"/>
       <c r="J106" s="15"/>
       <c r="K106" s="18"/>
     </row>
     <row r="107" spans="1:12" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="75" t="s">
+      <c r="A107" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="B107" s="76"/>
-      <c r="C107" s="76"/>
-      <c r="D107" s="76"/>
-      <c r="E107" s="76"/>
-      <c r="F107" s="76"/>
-      <c r="G107" s="77"/>
+      <c r="B107" s="80"/>
+      <c r="C107" s="80"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="80"/>
+      <c r="F107" s="80"/>
+      <c r="G107" s="81"/>
     </row>
     <row r="108" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="60" t="s">
+      <c r="A108" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="B108" s="61"/>
-      <c r="C108" s="61"/>
-      <c r="D108" s="61"/>
-      <c r="E108" s="61"/>
-      <c r="F108" s="61"/>
-      <c r="G108" s="62"/>
+      <c r="B108" s="64"/>
+      <c r="C108" s="64"/>
+      <c r="D108" s="64"/>
+      <c r="E108" s="64"/>
+      <c r="F108" s="64"/>
+      <c r="G108" s="65"/>
       <c r="H108" s="23"/>
       <c r="I108" s="23"/>
       <c r="J108" s="23"/>
@@ -5085,13 +7280,13 @@
       <c r="L108" s="23"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A109" s="60"/>
-      <c r="B109" s="61"/>
-      <c r="C109" s="61"/>
-      <c r="D109" s="61"/>
-      <c r="E109" s="61"/>
-      <c r="F109" s="61"/>
-      <c r="G109" s="62"/>
+      <c r="A109" s="63"/>
+      <c r="B109" s="64"/>
+      <c r="C109" s="64"/>
+      <c r="D109" s="64"/>
+      <c r="E109" s="64"/>
+      <c r="F109" s="64"/>
+      <c r="G109" s="65"/>
       <c r="H109" s="23"/>
       <c r="I109" s="23"/>
       <c r="J109" s="23"/>
@@ -5099,13 +7294,13 @@
       <c r="L109" s="23"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A110" s="60"/>
-      <c r="B110" s="61"/>
-      <c r="C110" s="61"/>
-      <c r="D110" s="61"/>
-      <c r="E110" s="61"/>
-      <c r="F110" s="61"/>
-      <c r="G110" s="62"/>
+      <c r="A110" s="63"/>
+      <c r="B110" s="64"/>
+      <c r="C110" s="64"/>
+      <c r="D110" s="64"/>
+      <c r="E110" s="64"/>
+      <c r="F110" s="64"/>
+      <c r="G110" s="65"/>
       <c r="H110" s="23"/>
       <c r="I110" s="23"/>
       <c r="J110" s="23"/>
@@ -5113,13 +7308,13 @@
       <c r="L110" s="23"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A111" s="60"/>
-      <c r="B111" s="61"/>
-      <c r="C111" s="61"/>
-      <c r="D111" s="61"/>
-      <c r="E111" s="61"/>
-      <c r="F111" s="61"/>
-      <c r="G111" s="62"/>
+      <c r="A111" s="63"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="64"/>
+      <c r="D111" s="64"/>
+      <c r="E111" s="64"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="65"/>
       <c r="H111" s="23"/>
       <c r="I111" s="23"/>
       <c r="J111" s="23"/>
@@ -5127,13 +7322,13 @@
       <c r="L111" s="23"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A112" s="60"/>
-      <c r="B112" s="61"/>
-      <c r="C112" s="61"/>
-      <c r="D112" s="61"/>
-      <c r="E112" s="61"/>
-      <c r="F112" s="61"/>
-      <c r="G112" s="62"/>
+      <c r="A112" s="63"/>
+      <c r="B112" s="64"/>
+      <c r="C112" s="64"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="65"/>
       <c r="H112" s="23"/>
       <c r="I112" s="23"/>
       <c r="J112" s="23"/>
@@ -5141,204 +7336,180 @@
       <c r="L112" s="23"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="82" t="s">
+      <c r="A113" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="B113" s="83"/>
-      <c r="C113" s="83"/>
-      <c r="D113" s="83"/>
-      <c r="E113" s="83"/>
-      <c r="F113" s="83"/>
-      <c r="G113" s="84"/>
+      <c r="B113" s="87"/>
+      <c r="C113" s="87"/>
+      <c r="D113" s="87"/>
+      <c r="E113" s="87"/>
+      <c r="F113" s="87"/>
+      <c r="G113" s="88"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="60" t="s">
+      <c r="A114" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B114" s="61"/>
-      <c r="C114" s="61"/>
-      <c r="D114" s="61"/>
-      <c r="E114" s="61"/>
-      <c r="F114" s="61"/>
-      <c r="G114" s="62"/>
+      <c r="B114" s="64"/>
+      <c r="C114" s="64"/>
+      <c r="D114" s="64"/>
+      <c r="E114" s="64"/>
+      <c r="F114" s="64"/>
+      <c r="G114" s="65"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B115" s="61" t="s">
+      <c r="B115" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="C115" s="61"/>
-      <c r="D115" s="61"/>
-      <c r="E115" s="61"/>
-      <c r="F115" s="61"/>
-      <c r="G115" s="62"/>
+      <c r="C115" s="64"/>
+      <c r="D115" s="64"/>
+      <c r="E115" s="64"/>
+      <c r="F115" s="64"/>
+      <c r="G115" s="65"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B116" s="61" t="s">
+      <c r="B116" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="C116" s="61"/>
-      <c r="D116" s="61"/>
-      <c r="E116" s="61"/>
-      <c r="F116" s="61"/>
-      <c r="G116" s="62"/>
+      <c r="C116" s="64"/>
+      <c r="D116" s="64"/>
+      <c r="E116" s="64"/>
+      <c r="F116" s="64"/>
+      <c r="G116" s="65"/>
     </row>
     <row r="117" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="60" t="s">
+      <c r="A117" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="B117" s="61"/>
-      <c r="C117" s="61"/>
-      <c r="D117" s="61"/>
-      <c r="E117" s="61"/>
-      <c r="F117" s="61"/>
-      <c r="G117" s="62"/>
+      <c r="B117" s="64"/>
+      <c r="C117" s="64"/>
+      <c r="D117" s="64"/>
+      <c r="E117" s="64"/>
+      <c r="F117" s="64"/>
+      <c r="G117" s="65"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="60"/>
-      <c r="B118" s="61"/>
-      <c r="C118" s="61"/>
-      <c r="D118" s="61"/>
-      <c r="E118" s="61"/>
-      <c r="F118" s="61"/>
-      <c r="G118" s="62"/>
+      <c r="A118" s="63"/>
+      <c r="B118" s="64"/>
+      <c r="C118" s="64"/>
+      <c r="D118" s="64"/>
+      <c r="E118" s="64"/>
+      <c r="F118" s="64"/>
+      <c r="G118" s="65"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="60"/>
-      <c r="B119" s="61"/>
-      <c r="C119" s="61"/>
-      <c r="D119" s="61"/>
-      <c r="E119" s="61"/>
-      <c r="F119" s="61"/>
-      <c r="G119" s="62"/>
+      <c r="A119" s="63"/>
+      <c r="B119" s="64"/>
+      <c r="C119" s="64"/>
+      <c r="D119" s="64"/>
+      <c r="E119" s="64"/>
+      <c r="F119" s="64"/>
+      <c r="G119" s="65"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="60"/>
-      <c r="B120" s="61"/>
-      <c r="C120" s="61"/>
-      <c r="D120" s="61"/>
-      <c r="E120" s="61"/>
-      <c r="F120" s="61"/>
-      <c r="G120" s="62"/>
+      <c r="A120" s="63"/>
+      <c r="B120" s="64"/>
+      <c r="C120" s="64"/>
+      <c r="D120" s="64"/>
+      <c r="E120" s="64"/>
+      <c r="F120" s="64"/>
+      <c r="G120" s="65"/>
     </row>
     <row r="121" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="85"/>
-      <c r="B121" s="86"/>
-      <c r="C121" s="86"/>
-      <c r="D121" s="86"/>
-      <c r="E121" s="86"/>
-      <c r="F121" s="86"/>
-      <c r="G121" s="87"/>
+      <c r="A121" s="89"/>
+      <c r="B121" s="90"/>
+      <c r="C121" s="90"/>
+      <c r="D121" s="90"/>
+      <c r="E121" s="90"/>
+      <c r="F121" s="90"/>
+      <c r="G121" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="195">
-    <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="A117:G121"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="D103:G103"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="D104:G106"/>
-    <mergeCell ref="A107:G107"/>
-    <mergeCell ref="A108:G112"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="D100:E100"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="D102:G102"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="D98:E98"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C90:E93"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A94:G94"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="D84:G86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="D81:G81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="D82:G82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="D83:G83"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="C70:E73"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="D63:G63"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:G66"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="D61:G61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C10:E13"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C30:E33"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
     <mergeCell ref="C50:E53"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="B51:B52"/>
@@ -5354,84 +7525,108 @@
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:E49"/>
     <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C30:E33"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:G26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C10:E13"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:G66"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="D61:G61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="C70:E73"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="D84:G86"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="D81:G81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="D82:G82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="D83:G83"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C90:E93"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A94:G94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="D102:G102"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="A117:G121"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="D103:G103"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="D104:G106"/>
+    <mergeCell ref="A107:G107"/>
+    <mergeCell ref="A108:G112"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
